--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/81.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/81.xlsx
@@ -426,13 +426,13 @@
         <v>-6.32691219453388</v>
       </c>
       <c r="E2">
-        <v>-14.36228381573452</v>
+        <v>-15.75702211077894</v>
       </c>
       <c r="F2">
-        <v>-3.812083150640817</v>
+        <v>-2.491450135053677</v>
       </c>
       <c r="G2">
-        <v>-10.40747903156904</v>
+        <v>-10.87392165587019</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-5.603674775703087</v>
       </c>
       <c r="E3">
-        <v>-15.0227934490713</v>
+        <v>-14.79137937033133</v>
       </c>
       <c r="F3">
-        <v>-4.049012795189531</v>
+        <v>-2.363073896804824</v>
       </c>
       <c r="G3">
-        <v>-10.22401190832817</v>
+        <v>-10.3957332159957</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-4.808745638449872</v>
       </c>
       <c r="E4">
-        <v>-15.11180513416607</v>
+        <v>-15.8073606278482</v>
       </c>
       <c r="F4">
-        <v>-3.702526591416166</v>
+        <v>-1.838052151808289</v>
       </c>
       <c r="G4">
-        <v>-10.78485473868164</v>
+        <v>-10.81643403258075</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-4.014047712523426</v>
       </c>
       <c r="E5">
-        <v>-15.96337561436046</v>
+        <v>-16.60688082779844</v>
       </c>
       <c r="F5">
-        <v>-3.657778184316936</v>
+        <v>-2.233959583200076</v>
       </c>
       <c r="G5">
-        <v>-10.34536988670677</v>
+        <v>-9.951285856257469</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-3.211274550721157</v>
       </c>
       <c r="E6">
-        <v>-17.08708474004581</v>
+        <v>-17.06923349550757</v>
       </c>
       <c r="F6">
-        <v>-3.610803954006385</v>
+        <v>-2.240685098143405</v>
       </c>
       <c r="G6">
-        <v>-9.589853736461999</v>
+        <v>-9.545942660429105</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-2.416687934474566</v>
       </c>
       <c r="E7">
-        <v>-16.40940313327195</v>
+        <v>-17.9922044253809</v>
       </c>
       <c r="F7">
-        <v>-3.570179159838291</v>
+        <v>-2.134761758347433</v>
       </c>
       <c r="G7">
-        <v>-9.124943894745527</v>
+        <v>-9.231414349834029</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-1.634095767476653</v>
       </c>
       <c r="E8">
-        <v>-17.40401905042063</v>
+        <v>-18.61489224380562</v>
       </c>
       <c r="F8">
-        <v>-3.060748117729846</v>
+        <v>-1.935532771034929</v>
       </c>
       <c r="G8">
-        <v>-7.61359378188421</v>
+        <v>-8.833119305458773</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-0.8829373344027334</v>
       </c>
       <c r="E9">
-        <v>-17.34510813205485</v>
+        <v>-19.31697779700681</v>
       </c>
       <c r="F9">
-        <v>-3.379458334119942</v>
+        <v>-1.825301092376996</v>
       </c>
       <c r="G9">
-        <v>-8.188963286064004</v>
+        <v>-8.090898306099712</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-0.1708781215661038</v>
       </c>
       <c r="E10">
-        <v>-18.76214916158704</v>
+        <v>-20.19898415100676</v>
       </c>
       <c r="F10">
-        <v>-3.640404006410619</v>
+        <v>-2.374820974943924</v>
       </c>
       <c r="G10">
-        <v>-7.203940255763714</v>
+        <v>-7.858577462335817</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>0.4816456773016582</v>
       </c>
       <c r="E11">
-        <v>-18.2964273092162</v>
+        <v>-20.72032472113981</v>
       </c>
       <c r="F11">
-        <v>-3.202045230727566</v>
+        <v>-1.661072284567577</v>
       </c>
       <c r="G11">
-        <v>-6.783722778827405</v>
+        <v>-6.439263826011778</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>1.057178194095252</v>
       </c>
       <c r="E12">
-        <v>-20.08910978615866</v>
+        <v>-21.60056949875078</v>
       </c>
       <c r="F12">
-        <v>-3.130269680377197</v>
+        <v>-1.541228230567559</v>
       </c>
       <c r="G12">
-        <v>-6.640230492973235</v>
+        <v>-6.282006291805318</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>1.546219215878271</v>
       </c>
       <c r="E13">
-        <v>-19.66940628665376</v>
+        <v>-21.57987890100973</v>
       </c>
       <c r="F13">
-        <v>-2.936936183870418</v>
+        <v>-1.896355134719526</v>
       </c>
       <c r="G13">
-        <v>-5.37061310484396</v>
+        <v>-5.305713170092087</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>1.93651170557844</v>
       </c>
       <c r="E14">
-        <v>-20.7718542268731</v>
+        <v>-22.08065567067395</v>
       </c>
       <c r="F14">
-        <v>-3.24920667207115</v>
+        <v>-1.485271184141049</v>
       </c>
       <c r="G14">
-        <v>-5.035807702820847</v>
+        <v>-5.008889657041033</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>2.229391804533918</v>
       </c>
       <c r="E15">
-        <v>-22.43645787345661</v>
+        <v>-23.43743629658607</v>
       </c>
       <c r="F15">
-        <v>-2.698308386145964</v>
+        <v>-1.368737286282618</v>
       </c>
       <c r="G15">
-        <v>-3.918104628397648</v>
+        <v>-4.225991984640947</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>2.438451162656146</v>
       </c>
       <c r="E16">
-        <v>-23.32508938492978</v>
+        <v>-22.97011136441652</v>
       </c>
       <c r="F16">
-        <v>-2.832216461910713</v>
+        <v>-1.329076711771383</v>
       </c>
       <c r="G16">
-        <v>-3.889187013112114</v>
+        <v>-3.717651095994777</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>2.579696379703702</v>
       </c>
       <c r="E17">
-        <v>-22.88328693226745</v>
+        <v>-24.55264094808501</v>
       </c>
       <c r="F17">
-        <v>-2.614261401090523</v>
+        <v>-1.027116084265893</v>
       </c>
       <c r="G17">
-        <v>-3.243514763860358</v>
+        <v>-3.459544413025499</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>2.675373932384707</v>
       </c>
       <c r="E18">
-        <v>-23.75304376407665</v>
+        <v>-25.33384799914823</v>
       </c>
       <c r="F18">
-        <v>-2.474296302876505</v>
+        <v>-0.6811500952214852</v>
       </c>
       <c r="G18">
-        <v>-3.009227456046136</v>
+        <v>-3.370818482027492</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>2.748185368600993</v>
       </c>
       <c r="E19">
-        <v>-24.3941126584985</v>
+        <v>-26.36502681543485</v>
       </c>
       <c r="F19">
-        <v>-1.920254362657695</v>
+        <v>-0.7662043750387301</v>
       </c>
       <c r="G19">
-        <v>-1.41651406546615</v>
+        <v>-2.836807623269814</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>2.81471139826032</v>
       </c>
       <c r="E20">
-        <v>-25.57084115786565</v>
+        <v>-26.16205155346304</v>
       </c>
       <c r="F20">
-        <v>-1.768058419741342</v>
+        <v>-0.4542693756361315</v>
       </c>
       <c r="G20">
-        <v>-1.851427054051284</v>
+        <v>-2.15351764505532</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>2.889434786395256</v>
       </c>
       <c r="E21">
-        <v>-25.80122727300588</v>
+        <v>-25.66774597315579</v>
       </c>
       <c r="F21">
-        <v>-1.642480406579145</v>
+        <v>-0.1260751808513841</v>
       </c>
       <c r="G21">
-        <v>-2.211462123629183</v>
+        <v>-1.955057061067091</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>2.981962576625701</v>
       </c>
       <c r="E22">
-        <v>-26.24235498304106</v>
+        <v>-27.6240603298914</v>
       </c>
       <c r="F22">
-        <v>-1.423186704036032</v>
+        <v>-0.2053068661943512</v>
       </c>
       <c r="G22">
-        <v>-1.789390741190882</v>
+        <v>-2.330188218304066</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>3.090942689108467</v>
       </c>
       <c r="E23">
-        <v>-25.99128279863379</v>
+        <v>-27.46491163936584</v>
       </c>
       <c r="F23">
-        <v>-1.668489486292244</v>
+        <v>0.2071008154937994</v>
       </c>
       <c r="G23">
-        <v>-1.022320787014051</v>
+        <v>-1.947969183067511</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>3.213546503163912</v>
       </c>
       <c r="E24">
-        <v>-26.67232000464734</v>
+        <v>-28.56204315110017</v>
       </c>
       <c r="F24">
-        <v>-1.035483423401571</v>
+        <v>0.4372419891765721</v>
       </c>
       <c r="G24">
-        <v>-1.762893134694555</v>
+        <v>-2.239826877809659</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>3.342860971239416</v>
       </c>
       <c r="E25">
-        <v>-26.29776539099892</v>
+        <v>-27.72775332771904</v>
       </c>
       <c r="F25">
-        <v>-1.307501054398067</v>
+        <v>0.1000227315383242</v>
       </c>
       <c r="G25">
-        <v>-0.2904121370098203</v>
+        <v>-2.151878925013381</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>3.46599095512649</v>
       </c>
       <c r="E26">
-        <v>-26.65990745739231</v>
+        <v>-27.82713521829137</v>
       </c>
       <c r="F26">
-        <v>-1.033193815900233</v>
+        <v>0.2730827642289885</v>
       </c>
       <c r="G26">
-        <v>-1.868761070494908</v>
+        <v>-2.376992711138282</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>3.574497328747269</v>
       </c>
       <c r="E27">
-        <v>-26.69943650700527</v>
+        <v>-28.9028923327095</v>
       </c>
       <c r="F27">
-        <v>-0.6846656864789663</v>
+        <v>0.5538504401012557</v>
       </c>
       <c r="G27">
-        <v>-2.024535480299775</v>
+        <v>-2.507825470850279</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>3.659042582271997</v>
       </c>
       <c r="E28">
-        <v>-26.25220894248175</v>
+        <v>-29.11949830144438</v>
       </c>
       <c r="F28">
-        <v>-0.6500995714949486</v>
+        <v>0.7220305604220282</v>
       </c>
       <c r="G28">
-        <v>-1.674259898971648</v>
+        <v>-2.590509656239116</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>3.708540228088522</v>
       </c>
       <c r="E29">
-        <v>-26.66934932569831</v>
+        <v>-28.90726683860091</v>
       </c>
       <c r="F29">
-        <v>-0.5405206463504215</v>
+        <v>0.618034003204967</v>
       </c>
       <c r="G29">
-        <v>-2.688673952569586</v>
+        <v>-2.740954087725756</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>3.716651839282616</v>
       </c>
       <c r="E30">
-        <v>-26.58635145408573</v>
+        <v>-28.09098675634829</v>
       </c>
       <c r="F30">
-        <v>-0.5443634427320084</v>
+        <v>0.6902195954197216</v>
       </c>
       <c r="G30">
-        <v>-3.955632972630826</v>
+        <v>-3.000788875466534</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>3.675582961240976</v>
       </c>
       <c r="E31">
-        <v>-25.24648467859225</v>
+        <v>-27.90938136321868</v>
       </c>
       <c r="F31">
-        <v>-1.017078756446172</v>
+        <v>0.4621501686113504</v>
       </c>
       <c r="G31">
-        <v>-2.687760242000747</v>
+        <v>-3.627637362781994</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>3.578000950696048</v>
       </c>
       <c r="E32">
-        <v>-26.2050629995879</v>
+        <v>-27.92424381491186</v>
       </c>
       <c r="F32">
-        <v>-0.6716594898876113</v>
+        <v>0.6040876096114345</v>
       </c>
       <c r="G32">
-        <v>-3.347224223969107</v>
+        <v>-3.535802829522611</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>3.422608449638553</v>
       </c>
       <c r="E33">
-        <v>-25.18341662108743</v>
+        <v>-26.55564840031372</v>
       </c>
       <c r="F33">
-        <v>-0.8714583939732409</v>
+        <v>0.8667430322214905</v>
       </c>
       <c r="G33">
-        <v>-3.679742039024583</v>
+        <v>-3.279053470224434</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>3.208258606121333</v>
       </c>
       <c r="E34">
-        <v>-25.05693634205319</v>
+        <v>-25.85776074251763</v>
       </c>
       <c r="F34">
-        <v>-0.7774652015123865</v>
+        <v>0.5959588402877629</v>
       </c>
       <c r="G34">
-        <v>-3.390277868707328</v>
+        <v>-3.102167711515635</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>2.936084899721763</v>
       </c>
       <c r="E35">
-        <v>-24.73427804053267</v>
+        <v>-26.62261094546514</v>
       </c>
       <c r="F35">
-        <v>-0.4581726428381227</v>
+        <v>0.3088798331735663</v>
       </c>
       <c r="G35">
-        <v>-3.881837602014932</v>
+        <v>-4.33880875552823</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>2.613445081358221</v>
       </c>
       <c r="E36">
-        <v>-22.93831241993465</v>
+        <v>-26.873438592276</v>
       </c>
       <c r="F36">
-        <v>-0.6311092487857699</v>
+        <v>0.8344019120813922</v>
       </c>
       <c r="G36">
-        <v>-4.784401564023053</v>
+        <v>-3.082175327003977</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>2.247032414868141</v>
       </c>
       <c r="E37">
-        <v>-22.19168479639401</v>
+        <v>-25.64552475120015</v>
       </c>
       <c r="F37">
-        <v>-0.684220853183663</v>
+        <v>0.04925043668593686</v>
       </c>
       <c r="G37">
-        <v>-4.436314253296384</v>
+        <v>-3.646798800363296</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>1.845208183922941</v>
       </c>
       <c r="E38">
-        <v>-24.25686366827403</v>
+        <v>-24.58417271260042</v>
       </c>
       <c r="F38">
-        <v>-0.7702111881660713</v>
+        <v>0.6648549855460006</v>
       </c>
       <c r="G38">
-        <v>-3.78418644024305</v>
+        <v>-3.603291610886194</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>1.419475890921721</v>
       </c>
       <c r="E39">
-        <v>-21.90872762649874</v>
+        <v>-23.62916735759683</v>
       </c>
       <c r="F39">
-        <v>-0.8111797548063264</v>
+        <v>0.8353495643901949</v>
       </c>
       <c r="G39">
-        <v>-3.987536699992782</v>
+        <v>-3.651824208491909</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>0.976802885820798</v>
       </c>
       <c r="E40">
-        <v>-21.27376311503923</v>
+        <v>-23.45904164607667</v>
       </c>
       <c r="F40">
-        <v>-0.7983417167977397</v>
+        <v>0.8676973114695156</v>
       </c>
       <c r="G40">
-        <v>-3.735776332822287</v>
+        <v>-3.324897904852262</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>0.5256122475159323</v>
       </c>
       <c r="E41">
-        <v>-21.93448558665437</v>
+        <v>-23.05262921778429</v>
       </c>
       <c r="F41">
-        <v>-0.5577631138396932</v>
+        <v>0.5893492967808257</v>
       </c>
       <c r="G41">
-        <v>-3.682873815104734</v>
+        <v>-3.552428389220831</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>0.0750582894708567</v>
       </c>
       <c r="E42">
-        <v>-19.26782121165355</v>
+        <v>-21.65848868130888</v>
       </c>
       <c r="F42">
-        <v>-0.6040398587970877</v>
+        <v>0.7194344569816544</v>
       </c>
       <c r="G42">
-        <v>-4.186083358165033</v>
+        <v>-4.178548556517652</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-0.3735278179410644</v>
       </c>
       <c r="E43">
-        <v>-19.33798085945439</v>
+        <v>-21.98601962086165</v>
       </c>
       <c r="F43">
-        <v>-0.8735475365631012</v>
+        <v>0.7187054936671909</v>
       </c>
       <c r="G43">
-        <v>-4.731297103027605</v>
+        <v>-3.721858799375191</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-0.8145141777883543</v>
       </c>
       <c r="E44">
-        <v>-19.90363254775249</v>
+        <v>-21.11065653823096</v>
       </c>
       <c r="F44">
-        <v>-0.4913404736462149</v>
+        <v>0.539078992574535</v>
       </c>
       <c r="G44">
-        <v>-4.482860523578537</v>
+        <v>-3.735451899359438</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.243955027048223</v>
       </c>
       <c r="E45">
-        <v>-18.87945928075574</v>
+        <v>-21.74431232070225</v>
       </c>
       <c r="F45">
-        <v>-0.4775009394476435</v>
+        <v>0.3362979658388272</v>
       </c>
       <c r="G45">
-        <v>-3.930128529796281</v>
+        <v>-3.643504807551721</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.664384277484205</v>
       </c>
       <c r="E46">
-        <v>-18.15010778555436</v>
+        <v>-20.20954908086666</v>
       </c>
       <c r="F46">
-        <v>-0.2491722336421962</v>
+        <v>1.007426324973736</v>
       </c>
       <c r="G46">
-        <v>-3.596140832521368</v>
+        <v>-4.408684440225628</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.072960902359145</v>
       </c>
       <c r="E47">
-        <v>-18.02416186645303</v>
+        <v>-19.28728006446451</v>
       </c>
       <c r="F47">
-        <v>-0.07253779560845205</v>
+        <v>0.4746154412886774</v>
       </c>
       <c r="G47">
-        <v>-4.368842024660498</v>
+        <v>-3.944046063243377</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.467889360865543</v>
       </c>
       <c r="E48">
-        <v>-16.72497890144447</v>
+        <v>-19.44383846785769</v>
       </c>
       <c r="F48">
-        <v>-0.4879814438278629</v>
+        <v>1.16905571587317</v>
       </c>
       <c r="G48">
-        <v>-4.650589313325712</v>
+        <v>-4.035731621953492</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.850191038500797</v>
       </c>
       <c r="E49">
-        <v>-16.98646657606938</v>
+        <v>-18.8959066983516</v>
       </c>
       <c r="F49">
-        <v>-0.261543072435604</v>
+        <v>0.8482754093434783</v>
       </c>
       <c r="G49">
-        <v>-4.101164554537188</v>
+        <v>-3.95788745414307</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.21544799838829</v>
       </c>
       <c r="E50">
-        <v>-15.6225083188551</v>
+        <v>-17.96713026480043</v>
       </c>
       <c r="F50">
-        <v>-0.07182788474425289</v>
+        <v>0.9297718511656994</v>
       </c>
       <c r="G50">
-        <v>-4.570424453092261</v>
+        <v>-5.119544641691172</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.562742513766623</v>
       </c>
       <c r="E51">
-        <v>-14.43440429278068</v>
+        <v>-17.28416392885962</v>
       </c>
       <c r="F51">
-        <v>-0.192214519393105</v>
+        <v>1.177205194381912</v>
       </c>
       <c r="G51">
-        <v>-4.576684694707022</v>
+        <v>-4.416450980060757</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.89230526769222</v>
       </c>
       <c r="E52">
-        <v>-14.49074756638412</v>
+        <v>-16.77863226148735</v>
       </c>
       <c r="F52">
-        <v>-0.2996106964312553</v>
+        <v>0.9550801320560298</v>
       </c>
       <c r="G52">
-        <v>-4.660246174663766</v>
+        <v>-4.690600566713344</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.197973752665789</v>
       </c>
       <c r="E53">
-        <v>-13.57042579380527</v>
+        <v>-16.19150654944487</v>
       </c>
       <c r="F53">
-        <v>0.06552868451834994</v>
+        <v>0.7796733345132345</v>
       </c>
       <c r="G53">
-        <v>-4.21334901122647</v>
+        <v>-3.902356363267335</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.48048983244188</v>
       </c>
       <c r="E54">
-        <v>-13.5700906867287</v>
+        <v>-15.41185276496629</v>
       </c>
       <c r="F54">
-        <v>-0.81917598534555</v>
+        <v>1.081999272043359</v>
       </c>
       <c r="G54">
-        <v>-5.384067161915557</v>
+        <v>-4.924619720338884</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.737992667781119</v>
       </c>
       <c r="E55">
-        <v>-12.65923342482589</v>
+        <v>-15.6663122479313</v>
       </c>
       <c r="F55">
-        <v>-0.258965193078092</v>
+        <v>1.068400792759002</v>
       </c>
       <c r="G55">
-        <v>-4.813150341486084</v>
+        <v>-4.804807766727121</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.963133630257428</v>
       </c>
       <c r="E56">
-        <v>-11.90859810178846</v>
+        <v>-14.41881275677227</v>
       </c>
       <c r="F56">
-        <v>-0.2644556122238471</v>
+        <v>0.7364491234351563</v>
       </c>
       <c r="G56">
-        <v>-5.343814238703559</v>
+        <v>-5.087018531767833</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.155751123968996</v>
       </c>
       <c r="E57">
-        <v>-12.33627624402086</v>
+        <v>-13.78820463730814</v>
       </c>
       <c r="F57">
-        <v>-0.04602258341224268</v>
+        <v>1.389636701360234</v>
       </c>
       <c r="G57">
-        <v>-5.077179590425119</v>
+        <v>-5.027951778256156</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.312448688264822</v>
       </c>
       <c r="E58">
-        <v>-12.16057145252325</v>
+        <v>-14.29360045046019</v>
       </c>
       <c r="F58">
-        <v>0.1291249351334764</v>
+        <v>0.7757336191455201</v>
       </c>
       <c r="G58">
-        <v>-5.566021365844981</v>
+        <v>-5.753583633917929</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.428335185075503</v>
       </c>
       <c r="E59">
-        <v>-10.6761331443349</v>
+        <v>-13.24100195211729</v>
       </c>
       <c r="F59">
-        <v>-0.6143911378624702</v>
+        <v>0.9387563240164628</v>
       </c>
       <c r="G59">
-        <v>-5.867837181569256</v>
+        <v>-6.109417621206493</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.506643972715824</v>
       </c>
       <c r="E60">
-        <v>-10.56277185450089</v>
+        <v>-13.11628777794605</v>
       </c>
       <c r="F60">
-        <v>-0.03465241244141667</v>
+        <v>0.8786135371036075</v>
       </c>
       <c r="G60">
-        <v>-6.051681707001603</v>
+        <v>-5.844716331522986</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.546143201087993</v>
       </c>
       <c r="E61">
-        <v>-11.0904658736667</v>
+        <v>-13.05290725573469</v>
       </c>
       <c r="F61">
-        <v>0.4630423203041655</v>
+        <v>1.097382054713346</v>
       </c>
       <c r="G61">
-        <v>-5.73986473320319</v>
+        <v>-6.605569081177065</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.5480300535528</v>
       </c>
       <c r="E62">
-        <v>-10.03873231385927</v>
+        <v>-12.34079113260651</v>
       </c>
       <c r="F62">
-        <v>-0.3960657968132298</v>
+        <v>1.095442018255989</v>
       </c>
       <c r="G62">
-        <v>-5.686372938379646</v>
+        <v>-6.283327199475487</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.520536902851851</v>
       </c>
       <c r="E63">
-        <v>-10.69019858460272</v>
+        <v>-12.24146358372227</v>
       </c>
       <c r="F63">
-        <v>-0.3317207020659726</v>
+        <v>0.47833563929465</v>
       </c>
       <c r="G63">
-        <v>-6.701008798528714</v>
+        <v>-6.623525480182073</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.463559742346292</v>
       </c>
       <c r="E64">
-        <v>-9.217172030913702</v>
+        <v>-12.81006330859936</v>
       </c>
       <c r="F64">
-        <v>-0.1976759456797622</v>
+        <v>1.022404864351157</v>
       </c>
       <c r="G64">
-        <v>-6.751451580910589</v>
+        <v>-6.956927210896534</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.383280555025276</v>
       </c>
       <c r="E65">
-        <v>-10.38892826582043</v>
+        <v>-11.89176576390195</v>
       </c>
       <c r="F65">
-        <v>-0.8600103564665517</v>
+        <v>1.01363245355551</v>
       </c>
       <c r="G65">
-        <v>-6.589304370942626</v>
+        <v>-6.905193315754343</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.288194787638875</v>
       </c>
       <c r="E66">
-        <v>-9.853653581165778</v>
+        <v>-11.49821873026535</v>
       </c>
       <c r="F66">
-        <v>-0.489175121255297</v>
+        <v>1.060927262050945</v>
       </c>
       <c r="G66">
-        <v>-6.504018096759922</v>
+        <v>-6.254671117287555</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.178947794196849</v>
       </c>
       <c r="E67">
-        <v>-11.08351919453893</v>
+        <v>-11.86795957604362</v>
       </c>
       <c r="F67">
-        <v>-0.2379611092127077</v>
+        <v>0.6675836277708223</v>
       </c>
       <c r="G67">
-        <v>-6.433635898595016</v>
+        <v>-7.453598426516773</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.06319695642502</v>
       </c>
       <c r="E68">
-        <v>-10.27543112176619</v>
+        <v>-12.05907476458933</v>
       </c>
       <c r="F68">
-        <v>-0.7454603985378249</v>
+        <v>0.6232957929475494</v>
       </c>
       <c r="G68">
-        <v>-5.971129512940057</v>
+        <v>-7.126291410140109</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.944906359048042</v>
       </c>
       <c r="E69">
-        <v>-10.55872339873803</v>
+        <v>-11.2877171444928</v>
       </c>
       <c r="F69">
-        <v>-0.7190702698194382</v>
+        <v>0.8573046140339929</v>
       </c>
       <c r="G69">
-        <v>-6.86178213209788</v>
+        <v>-6.959188313499856</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.822380206791122</v>
       </c>
       <c r="E70">
-        <v>-10.72216055414886</v>
+        <v>-12.16135940700059</v>
       </c>
       <c r="F70">
-        <v>-0.1849108040026218</v>
+        <v>0.729967976875653</v>
       </c>
       <c r="G70">
-        <v>-6.50602759790226</v>
+        <v>-7.227981437469902</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.701619042294636</v>
       </c>
       <c r="E71">
-        <v>-9.996631091009954</v>
+        <v>-10.55214805447889</v>
       </c>
       <c r="F71">
-        <v>-0.1362259950052893</v>
+        <v>0.09940145598622452</v>
       </c>
       <c r="G71">
-        <v>-6.646348381129808</v>
+        <v>-6.796425342061589</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.581170537722466</v>
       </c>
       <c r="E72">
-        <v>-10.73500783490862</v>
+        <v>-11.38185959063826</v>
       </c>
       <c r="F72">
-        <v>-0.7429636991857871</v>
+        <v>0.5767084102141052</v>
       </c>
       <c r="G72">
-        <v>-6.660080524026704</v>
+        <v>-6.671011945397378</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.457833767608248</v>
       </c>
       <c r="E73">
-        <v>-9.739576792438553</v>
+        <v>-11.68871351787201</v>
       </c>
       <c r="F73">
-        <v>-0.3247599307802483</v>
+        <v>0.486710433736953</v>
       </c>
       <c r="G73">
-        <v>-7.101915863334455</v>
+        <v>-6.251072554286368</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.335289830104602</v>
       </c>
       <c r="E74">
-        <v>-11.70036075301974</v>
+        <v>-11.88982304855266</v>
       </c>
       <c r="F74">
-        <v>-0.6138833486445542</v>
+        <v>0.7432500198121402</v>
       </c>
       <c r="G74">
-        <v>-7.033702072497772</v>
+        <v>-6.465791227417958</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.207500581913123</v>
       </c>
       <c r="E75">
-        <v>-11.54930897401989</v>
+        <v>-11.09715442977603</v>
       </c>
       <c r="F75">
-        <v>0.114719625998793</v>
+        <v>0.5460621297801348</v>
       </c>
       <c r="G75">
-        <v>-5.430249272188391</v>
+        <v>-5.75657636708543</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.072674206774768</v>
       </c>
       <c r="E76">
-        <v>-11.69084190065562</v>
+        <v>-12.2271943621241</v>
       </c>
       <c r="F76">
-        <v>-0.7279346293967957</v>
+        <v>0.4987656645498942</v>
       </c>
       <c r="G76">
-        <v>-5.648622787595336</v>
+        <v>-6.399325404626009</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.93149551963791</v>
       </c>
       <c r="E77">
-        <v>-11.8523001129251</v>
+        <v>-13.3237190583414</v>
       </c>
       <c r="F77">
-        <v>-0.3055857105076482</v>
+        <v>0.3571661974501523</v>
       </c>
       <c r="G77">
-        <v>-5.125715498576374</v>
+        <v>-6.029173307880098</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.778046076814624</v>
       </c>
       <c r="E78">
-        <v>-12.04487799857529</v>
+        <v>-14.49447450049243</v>
       </c>
       <c r="F78">
-        <v>-0.5857039463361206</v>
+        <v>0.4893786051413702</v>
       </c>
       <c r="G78">
-        <v>-5.452711323672346</v>
+        <v>-5.876053955597728</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.611795591071055</v>
       </c>
       <c r="E79">
-        <v>-14.1824399989939</v>
+        <v>-13.05714137893187</v>
       </c>
       <c r="F79">
-        <v>-0.4495369126639379</v>
+        <v>-0.07286914256957186</v>
       </c>
       <c r="G79">
-        <v>-5.243276281221433</v>
+        <v>-5.522355270181993</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.430437796222796</v>
       </c>
       <c r="E80">
-        <v>-13.07871955757841</v>
+        <v>-15.08444862268573</v>
       </c>
       <c r="F80">
-        <v>-0.8520779102173436</v>
+        <v>0.06886203494721516</v>
       </c>
       <c r="G80">
-        <v>-5.368017637141171</v>
+        <v>-5.897539396147597</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.227686019723931</v>
       </c>
       <c r="E81">
-        <v>-14.35920898188332</v>
+        <v>-15.84789499869086</v>
       </c>
       <c r="F81">
-        <v>-0.531090511836952</v>
+        <v>0.5128545373367082</v>
       </c>
       <c r="G81">
-        <v>-5.093646243937454</v>
+        <v>-4.440459056311552</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.003681080052863</v>
       </c>
       <c r="E82">
-        <v>-16.88315397005839</v>
+        <v>-16.41070280531215</v>
       </c>
       <c r="F82">
-        <v>-0.4263625062032189</v>
+        <v>0.1089160839747796</v>
       </c>
       <c r="G82">
-        <v>-4.74435389463449</v>
+        <v>-4.93585902244471</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.755926087561225</v>
       </c>
       <c r="E83">
-        <v>-15.83267026907707</v>
+        <v>-17.49428512281553</v>
       </c>
       <c r="F83">
-        <v>-0.8298760070875113</v>
+        <v>0.2264937247607387</v>
       </c>
       <c r="G83">
-        <v>-4.49225254127345</v>
+        <v>-4.210809822797849</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.48121134415128</v>
       </c>
       <c r="E84">
-        <v>-17.82512637686791</v>
+        <v>-18.42526239473442</v>
       </c>
       <c r="F84">
-        <v>-0.7607586877327261</v>
+        <v>0.154494515211614</v>
       </c>
       <c r="G84">
-        <v>-3.264933993499442</v>
+        <v>-4.345201418964563</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.184405898093378</v>
       </c>
       <c r="E85">
-        <v>-18.64201327463756</v>
+        <v>-18.89312168683688</v>
       </c>
       <c r="F85">
-        <v>-0.9331154364984137</v>
+        <v>0.04368215100431858</v>
       </c>
       <c r="G85">
-        <v>-3.809740541260684</v>
+        <v>-4.674421930662925</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-1.867299043085168</v>
       </c>
       <c r="E86">
-        <v>-19.34348295537371</v>
+        <v>-20.58415350772917</v>
       </c>
       <c r="F86">
-        <v>-0.4838603159989354</v>
+        <v>0.111657980078046</v>
       </c>
       <c r="G86">
-        <v>-3.160502834463133</v>
+        <v>-4.080927189655623</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-1.535176776471996</v>
       </c>
       <c r="E87">
-        <v>-21.89653244599608</v>
+        <v>-22.75487299483195</v>
       </c>
       <c r="F87">
-        <v>-0.5559282800424924</v>
+        <v>0.2753085874403107</v>
       </c>
       <c r="G87">
-        <v>-2.626587981526094</v>
+        <v>-3.756970445364701</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-1.198025019110076</v>
       </c>
       <c r="E88">
-        <v>-22.2872627687999</v>
+        <v>-22.47408496398634</v>
       </c>
       <c r="F88">
-        <v>-0.8178580528076961</v>
+        <v>0.5185429362917324</v>
       </c>
       <c r="G88">
-        <v>-2.222234638813972</v>
+        <v>-3.156377894721201</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.863594302441455</v>
       </c>
       <c r="E89">
-        <v>-25.29873421169275</v>
+        <v>-25.31625487762843</v>
       </c>
       <c r="F89">
-        <v>-0.5222269806269972</v>
+        <v>0.05550792404668432</v>
       </c>
       <c r="G89">
-        <v>-2.516297156885274</v>
+        <v>-2.732535370419389</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.5452174139804238</v>
       </c>
       <c r="E90">
-        <v>-25.73690935667494</v>
+        <v>-26.02067712341758</v>
       </c>
       <c r="F90">
-        <v>-0.5393973801522254</v>
+        <v>-0.01130322045870701</v>
       </c>
       <c r="G90">
-        <v>-1.707511018368087</v>
+        <v>-2.007837088599691</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-0.2561784800234277</v>
       </c>
       <c r="E91">
-        <v>-27.30976611986305</v>
+        <v>-27.61399353217235</v>
       </c>
       <c r="F91">
-        <v>-0.8469370621155698</v>
+        <v>-0.187839082771518</v>
       </c>
       <c r="G91">
-        <v>-2.783531013906323</v>
+        <v>-2.635215263201435</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-0.007877105475397501</v>
       </c>
       <c r="E92">
-        <v>-29.45889384289726</v>
+        <v>-29.61451485217085</v>
       </c>
       <c r="F92">
-        <v>-1.030728594509502</v>
+        <v>-0.4191449410226268</v>
       </c>
       <c r="G92">
-        <v>-2.815189760898373</v>
+        <v>-2.118591389616009</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>0.183015629931366</v>
       </c>
       <c r="E93">
-        <v>-30.8661624255209</v>
+        <v>-31.44488102556813</v>
       </c>
       <c r="F93">
-        <v>-0.5580737516157431</v>
+        <v>-0.2731567834228531</v>
       </c>
       <c r="G93">
-        <v>-1.765938836590685</v>
+        <v>-2.817709086053759</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>0.3057036178961994</v>
       </c>
       <c r="E94">
-        <v>-33.5417388373688</v>
+        <v>-32.40189023032012</v>
       </c>
       <c r="F94">
-        <v>-1.319342566421086</v>
+        <v>-0.4494615312302831</v>
       </c>
       <c r="G94">
-        <v>-1.660236428067295</v>
+        <v>-2.120336047115205</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>0.3516840929332225</v>
       </c>
       <c r="E95">
-        <v>-35.64754717804563</v>
+        <v>-36.21295432874732</v>
       </c>
       <c r="F95">
-        <v>-1.669747776377096</v>
+        <v>-0.5117398493075556</v>
       </c>
       <c r="G95">
-        <v>-2.699429915026678</v>
+        <v>-2.537537617065238</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>0.3072902641513354</v>
       </c>
       <c r="E96">
-        <v>-37.29190854581486</v>
+        <v>-37.85749909971386</v>
       </c>
       <c r="F96">
-        <v>-1.431930121972581</v>
+        <v>-1.041858538933516</v>
       </c>
       <c r="G96">
-        <v>-2.444445076500932</v>
+        <v>-2.331270766695408</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>0.1781695337823656</v>
       </c>
       <c r="E97">
-        <v>-39.78144845271666</v>
+        <v>-40.83827881001973</v>
       </c>
       <c r="F97">
-        <v>-1.915632900917476</v>
+        <v>-1.062070703561824</v>
       </c>
       <c r="G97">
-        <v>-2.095248733018607</v>
+        <v>-2.655455938628538</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-0.05044377044744228</v>
       </c>
       <c r="E98">
-        <v>-43.49332764919087</v>
+        <v>-42.62485463976284</v>
       </c>
       <c r="F98">
-        <v>-2.324207726632874</v>
+        <v>-1.304379766024318</v>
       </c>
       <c r="G98">
-        <v>-2.28220186071233</v>
+        <v>-2.506170198080643</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-0.3545087522072987</v>
       </c>
       <c r="E99">
-        <v>-44.6986217625984</v>
+        <v>-44.45047044392608</v>
       </c>
       <c r="F99">
-        <v>-2.959087556588679</v>
+        <v>-2.004130704028159</v>
       </c>
       <c r="G99">
-        <v>-2.678258976303038</v>
+        <v>-3.107984340028135</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-0.7593844943998388</v>
       </c>
       <c r="E100">
-        <v>-47.0187197575552</v>
+        <v>-47.68517074879004</v>
       </c>
       <c r="F100">
-        <v>-2.894546967134362</v>
+        <v>-2.415241990730928</v>
       </c>
       <c r="G100">
-        <v>-3.366547878281832</v>
+        <v>-2.751988136008147</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-1.205499106813494</v>
       </c>
       <c r="E101">
-        <v>-49.54160281857548</v>
+        <v>-49.3809167111243</v>
       </c>
       <c r="F101">
-        <v>-3.345779400624322</v>
+        <v>-2.331409552832813</v>
       </c>
       <c r="G101">
-        <v>-3.79408828195101</v>
+        <v>-4.058196983982986</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-1.769347643511443</v>
       </c>
       <c r="E102">
-        <v>-51.72798063667828</v>
+        <v>-52.30987256488638</v>
       </c>
       <c r="F102">
-        <v>-3.514179038306836</v>
+        <v>-2.686794079247051</v>
       </c>
       <c r="G102">
-        <v>-4.566325997714642</v>
+        <v>-4.148862894667007</v>
       </c>
     </row>
   </sheetData>
